--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_DB61266FACF10F39B66C813355FDBEEA58404ACA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DFC8C62-3FAC-4ADF-80CD-EB6463F7C8F7}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_D49781AC3DCA5FE5FFCC362AE99D049711BC364F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4242842C-5A0F-45C4-936D-A21259A96D63}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,11 +32,15 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,7 +74,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -96,44 +97,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -163,12 +164,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -207,155 +208,227 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="3" ht="15.75" x14ac:dyDescent="0.25"/>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00a272c57818f5a2598402ed9b64a3e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb7fe868ff501d2f097cc8d8c004abe7" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -616,29 +689,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
     <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72BDBC8C-268D-46DC-950E-B83A27DCD0DB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCDFE4C4-5B96-4C00-9C27-BAA4B256509C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0E60A91-C509-4872-9DF7-38C7066FAABE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -656,8 +728,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65580776-39A1-4F81-92E4-469352F66D91}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82A14EE1-59CC-47A3-BB1A-D631CBDCDEB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -665,12 +737,4 @@
     <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8384541B-BAD0-4494-AED6-1A7611440316}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -1,44 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_D49781AC3DCA5FE5FFCC362AE99D049711BC364F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4242842C-5A0F-45C4-936D-A21259A96D63}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Supplement" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -68,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -407,28 +396,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
   <sheetData>
-    <row r="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>RPRO</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Giới tính</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Mã khuôn</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Mã dao</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Tên vải</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BOM</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Total</v>
+      </c>
+      <c r="H1" t="str">
+        <v>#1</v>
+      </c>
+      <c r="I1" t="str">
+        <v>#1.5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>RPRO-250520-0723</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>OV-0256</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>18-4006TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
+      </c>
+      <c r="F2" t="str">
+        <v>OV-007152</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00a272c57818f5a2598402ed9b64a3e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb7fe868ff501d2f097cc8d8c004abe7" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -689,6 +725,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -702,39 +747,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCDFE4C4-5B96-4C00-9C27-BAA4B256509C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E74DBB5-450F-46AE-9A6C-64D1DAFE42AA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0E60A91-C509-4872-9DF7-38C7066FAABE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D5024B9-9658-42F2-8189-5FCDE05BA8D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82A14EE1-59CC-47A3-BB1A-D631CBDCDEB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A270006-58F0-405B-8DB7-6F38FA9CED72}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:CA5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,39 +427,454 @@
       <c r="I1" t="str">
         <v>#1.5</v>
       </c>
+      <c r="J1" t="str">
+        <v>#2</v>
+      </c>
+      <c r="K1" t="str">
+        <v>#2.5</v>
+      </c>
+      <c r="L1" t="str">
+        <v>#3</v>
+      </c>
+      <c r="M1" t="str">
+        <v>#3.5</v>
+      </c>
+      <c r="N1" t="str">
+        <v>#4</v>
+      </c>
+      <c r="O1" t="str">
+        <v>#4.5</v>
+      </c>
+      <c r="P1" t="str">
+        <v>#5</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>#5.5</v>
+      </c>
+      <c r="R1" t="str">
+        <v>#6</v>
+      </c>
+      <c r="S1" t="str">
+        <v>#6.5</v>
+      </c>
+      <c r="T1" t="str">
+        <v>#7</v>
+      </c>
+      <c r="U1" t="str">
+        <v>#7.5</v>
+      </c>
+      <c r="V1" t="str">
+        <v>#8</v>
+      </c>
+      <c r="W1" t="str">
+        <v>#8.5</v>
+      </c>
+      <c r="X1" t="str">
+        <v>#9</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>#9.5</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>#10</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>#10.5</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>#11</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>#11.5</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>#12</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>#12.5</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>#13</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>#13.5</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>#14</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>#14.5</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>#15</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>#15.5</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>#16</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>#16.5</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>#17</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>#17.5</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>#18</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>#18.5</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>#19</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>#19.5</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>#20</v>
+      </c>
+      <c r="AU1" t="str">
+        <v>#20.5</v>
+      </c>
+      <c r="AV1" t="str">
+        <v>#21</v>
+      </c>
+      <c r="AW1" t="str">
+        <v>#22</v>
+      </c>
+      <c r="AX1" t="str">
+        <v>#23</v>
+      </c>
+      <c r="AY1" t="str">
+        <v>#24</v>
+      </c>
+      <c r="AZ1" t="str">
+        <v>#25</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>#26</v>
+      </c>
+      <c r="BB1" t="str">
+        <v>#27</v>
+      </c>
+      <c r="BC1" t="str">
+        <v>#28</v>
+      </c>
+      <c r="BD1" t="str">
+        <v>#29</v>
+      </c>
+      <c r="BE1" t="str">
+        <v>#30</v>
+      </c>
+      <c r="BF1" t="str">
+        <v>#31</v>
+      </c>
+      <c r="BG1" t="str">
+        <v>#32</v>
+      </c>
+      <c r="BH1" t="str">
+        <v>#33</v>
+      </c>
+      <c r="BI1" t="str">
+        <v>#34</v>
+      </c>
+      <c r="BJ1" t="str">
+        <v>#35</v>
+      </c>
+      <c r="BK1" t="str">
+        <v>#36</v>
+      </c>
+      <c r="BL1" t="str">
+        <v>#37</v>
+      </c>
+      <c r="BM1" t="str">
+        <v>#38</v>
+      </c>
+      <c r="BN1" t="str">
+        <v>#39</v>
+      </c>
+      <c r="BO1" t="str">
+        <v>#40</v>
+      </c>
+      <c r="BP1" t="str">
+        <v>#41</v>
+      </c>
+      <c r="BQ1" t="str">
+        <v>#42</v>
+      </c>
+      <c r="BR1" t="str">
+        <v>#43</v>
+      </c>
+      <c r="BS1" t="str">
+        <v>#44</v>
+      </c>
+      <c r="BT1" t="str">
+        <v>#45</v>
+      </c>
+      <c r="BU1" t="str">
+        <v>#46</v>
+      </c>
+      <c r="BV1" t="str">
+        <v>#47</v>
+      </c>
+      <c r="BW1" t="str">
+        <v>#48</v>
+      </c>
+      <c r="BX1" t="str">
+        <v>#49</v>
+      </c>
+      <c r="BY1" t="str">
+        <v>#50</v>
+      </c>
+      <c r="BZ1" t="str">
+        <v>134.9mm*355mm</v>
+      </c>
+      <c r="CA1" t="str">
+        <v>134.9mm*390mm</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
+    <row r="5">
+      <c r="A5" t="str">
         <v>RPRO-250520-0723</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B5" t="str">
         <v/>
       </c>
-      <c r="C2" t="str">
+      <c r="C5" t="str">
         <v>OV-0256</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D5" t="str">
         <v/>
       </c>
-      <c r="E2" t="str">
+      <c r="E5" t="str">
         <v>18-4006TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F5" t="str">
         <v>OV-007152</v>
       </c>
-      <c r="G2">
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>5</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CA5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -747,13 +1162,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E74DBB5-450F-46AE-9A6C-64D1DAFE42AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302E30A6-07D0-47DA-98EE-1574F0A3E92A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D5024B9-9658-42F2-8189-5FCDE05BA8D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6FBA6A7-5B2B-4104-81BE-7CAC68298164}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A270006-58F0-405B-8DB7-6F38FA9CED72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2156788C-9D3E-46C2-BACF-CE7A024B2948}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -1,42 +1,306 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_764F018385AADDC0ADE7E0A24F7E0D0B11BCC454" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{157A9C2F-175C-4CAA-B67F-EB6091841A35}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Supplement" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="84">
+  <si>
+    <t>RPRO</t>
+  </si>
+  <si>
+    <t>Giới tính</t>
+  </si>
+  <si>
+    <t>Mã khuôn</t>
+  </si>
+  <si>
+    <t>Mã dao</t>
+  </si>
+  <si>
+    <t>Tên vải</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>#1</t>
+  </si>
+  <si>
+    <t>#1.5</t>
+  </si>
+  <si>
+    <t>#2</t>
+  </si>
+  <si>
+    <t>#2.5</t>
+  </si>
+  <si>
+    <t>#3</t>
+  </si>
+  <si>
+    <t>#3.5</t>
+  </si>
+  <si>
+    <t>#4</t>
+  </si>
+  <si>
+    <t>#4.5</t>
+  </si>
+  <si>
+    <t>#5</t>
+  </si>
+  <si>
+    <t>#5.5</t>
+  </si>
+  <si>
+    <t>#6</t>
+  </si>
+  <si>
+    <t>#6.5</t>
+  </si>
+  <si>
+    <t>#7</t>
+  </si>
+  <si>
+    <t>#7.5</t>
+  </si>
+  <si>
+    <t>#8</t>
+  </si>
+  <si>
+    <t>#8.5</t>
+  </si>
+  <si>
+    <t>#9</t>
+  </si>
+  <si>
+    <t>#9.5</t>
+  </si>
+  <si>
+    <t>#10</t>
+  </si>
+  <si>
+    <t>#10.5</t>
+  </si>
+  <si>
+    <t>#11</t>
+  </si>
+  <si>
+    <t>#11.5</t>
+  </si>
+  <si>
+    <t>#12</t>
+  </si>
+  <si>
+    <t>#12.5</t>
+  </si>
+  <si>
+    <t>#13</t>
+  </si>
+  <si>
+    <t>#13.5</t>
+  </si>
+  <si>
+    <t>#14</t>
+  </si>
+  <si>
+    <t>#14.5</t>
+  </si>
+  <si>
+    <t>#15</t>
+  </si>
+  <si>
+    <t>#15.5</t>
+  </si>
+  <si>
+    <t>#16</t>
+  </si>
+  <si>
+    <t>#16.5</t>
+  </si>
+  <si>
+    <t>#17</t>
+  </si>
+  <si>
+    <t>#17.5</t>
+  </si>
+  <si>
+    <t>#18</t>
+  </si>
+  <si>
+    <t>#18.5</t>
+  </si>
+  <si>
+    <t>#19</t>
+  </si>
+  <si>
+    <t>#19.5</t>
+  </si>
+  <si>
+    <t>#20</t>
+  </si>
+  <si>
+    <t>#20.5</t>
+  </si>
+  <si>
+    <t>#21</t>
+  </si>
+  <si>
+    <t>#22</t>
+  </si>
+  <si>
+    <t>#23</t>
+  </si>
+  <si>
+    <t>#24</t>
+  </si>
+  <si>
+    <t>#25</t>
+  </si>
+  <si>
+    <t>#26</t>
+  </si>
+  <si>
+    <t>#27</t>
+  </si>
+  <si>
+    <t>#28</t>
+  </si>
+  <si>
+    <t>#29</t>
+  </si>
+  <si>
+    <t>#30</t>
+  </si>
+  <si>
+    <t>#31</t>
+  </si>
+  <si>
+    <t>#32</t>
+  </si>
+  <si>
+    <t>#33</t>
+  </si>
+  <si>
+    <t>#34</t>
+  </si>
+  <si>
+    <t>#35</t>
+  </si>
+  <si>
+    <t>#36</t>
+  </si>
+  <si>
+    <t>#37</t>
+  </si>
+  <si>
+    <t>#38</t>
+  </si>
+  <si>
+    <t>#39</t>
+  </si>
+  <si>
+    <t>#40</t>
+  </si>
+  <si>
+    <t>#41</t>
+  </si>
+  <si>
+    <t>#42</t>
+  </si>
+  <si>
+    <t>#43</t>
+  </si>
+  <si>
+    <t>#44</t>
+  </si>
+  <si>
+    <t>#45</t>
+  </si>
+  <si>
+    <t>#46</t>
+  </si>
+  <si>
+    <t>#47</t>
+  </si>
+  <si>
+    <t>#48</t>
+  </si>
+  <si>
+    <t>#49</t>
+  </si>
+  <si>
+    <t>#50</t>
+  </si>
+  <si>
+    <t>134.9mm*355mm</t>
+  </si>
+  <si>
+    <t>134.9mm*390mm</t>
+  </si>
+  <si>
+    <t>RPRO-250520-0723</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>OV-0256</t>
+  </si>
+  <si>
+    <t>18-4006TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-007152</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -64,14 +328,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,490 +674,515 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CA5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CA2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>RPRO</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Giới tính</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Mã khuôn</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Mã dao</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Tên vải</v>
-      </c>
-      <c r="F1" t="str">
-        <v>BOM</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Total</v>
-      </c>
-      <c r="H1" t="str">
-        <v>#1</v>
-      </c>
-      <c r="I1" t="str">
-        <v>#1.5</v>
-      </c>
-      <c r="J1" t="str">
-        <v>#2</v>
-      </c>
-      <c r="K1" t="str">
-        <v>#2.5</v>
-      </c>
-      <c r="L1" t="str">
-        <v>#3</v>
-      </c>
-      <c r="M1" t="str">
-        <v>#3.5</v>
-      </c>
-      <c r="N1" t="str">
-        <v>#4</v>
-      </c>
-      <c r="O1" t="str">
-        <v>#4.5</v>
-      </c>
-      <c r="P1" t="str">
-        <v>#5</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>#5.5</v>
-      </c>
-      <c r="R1" t="str">
-        <v>#6</v>
-      </c>
-      <c r="S1" t="str">
-        <v>#6.5</v>
-      </c>
-      <c r="T1" t="str">
-        <v>#7</v>
-      </c>
-      <c r="U1" t="str">
-        <v>#7.5</v>
-      </c>
-      <c r="V1" t="str">
-        <v>#8</v>
-      </c>
-      <c r="W1" t="str">
-        <v>#8.5</v>
-      </c>
-      <c r="X1" t="str">
-        <v>#9</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>#9.5</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>#10</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>#10.5</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>#11</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>#11.5</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>#12</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>#12.5</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>#13</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>#13.5</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>#14</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>#14.5</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>#15</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>#15.5</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>#16</v>
-      </c>
-      <c r="AM1" t="str">
-        <v>#16.5</v>
-      </c>
-      <c r="AN1" t="str">
-        <v>#17</v>
-      </c>
-      <c r="AO1" t="str">
-        <v>#17.5</v>
-      </c>
-      <c r="AP1" t="str">
-        <v>#18</v>
-      </c>
-      <c r="AQ1" t="str">
-        <v>#18.5</v>
-      </c>
-      <c r="AR1" t="str">
-        <v>#19</v>
-      </c>
-      <c r="AS1" t="str">
-        <v>#19.5</v>
-      </c>
-      <c r="AT1" t="str">
-        <v>#20</v>
-      </c>
-      <c r="AU1" t="str">
-        <v>#20.5</v>
-      </c>
-      <c r="AV1" t="str">
-        <v>#21</v>
-      </c>
-      <c r="AW1" t="str">
-        <v>#22</v>
-      </c>
-      <c r="AX1" t="str">
-        <v>#23</v>
-      </c>
-      <c r="AY1" t="str">
-        <v>#24</v>
-      </c>
-      <c r="AZ1" t="str">
-        <v>#25</v>
-      </c>
-      <c r="BA1" t="str">
-        <v>#26</v>
-      </c>
-      <c r="BB1" t="str">
-        <v>#27</v>
-      </c>
-      <c r="BC1" t="str">
-        <v>#28</v>
-      </c>
-      <c r="BD1" t="str">
-        <v>#29</v>
-      </c>
-      <c r="BE1" t="str">
-        <v>#30</v>
-      </c>
-      <c r="BF1" t="str">
-        <v>#31</v>
-      </c>
-      <c r="BG1" t="str">
-        <v>#32</v>
-      </c>
-      <c r="BH1" t="str">
-        <v>#33</v>
-      </c>
-      <c r="BI1" t="str">
-        <v>#34</v>
-      </c>
-      <c r="BJ1" t="str">
-        <v>#35</v>
-      </c>
-      <c r="BK1" t="str">
-        <v>#36</v>
-      </c>
-      <c r="BL1" t="str">
-        <v>#37</v>
-      </c>
-      <c r="BM1" t="str">
-        <v>#38</v>
-      </c>
-      <c r="BN1" t="str">
-        <v>#39</v>
-      </c>
-      <c r="BO1" t="str">
-        <v>#40</v>
-      </c>
-      <c r="BP1" t="str">
-        <v>#41</v>
-      </c>
-      <c r="BQ1" t="str">
-        <v>#42</v>
-      </c>
-      <c r="BR1" t="str">
-        <v>#43</v>
-      </c>
-      <c r="BS1" t="str">
-        <v>#44</v>
-      </c>
-      <c r="BT1" t="str">
-        <v>#45</v>
-      </c>
-      <c r="BU1" t="str">
-        <v>#46</v>
-      </c>
-      <c r="BV1" t="str">
-        <v>#47</v>
-      </c>
-      <c r="BW1" t="str">
-        <v>#48</v>
-      </c>
-      <c r="BX1" t="str">
-        <v>#49</v>
-      </c>
-      <c r="BY1" t="str">
-        <v>#50</v>
-      </c>
-      <c r="BZ1" t="str">
-        <v>134.9mm*355mm</v>
-      </c>
-      <c r="CA1" t="str">
-        <v>134.9mm*390mm</v>
+    <row r="1" spans="1:79" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>RPRO-250520-0723</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>18-4006TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F5" t="str">
-        <v>OV-007152</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2">
         <v>2</v>
       </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5">
-        <v>0</v>
-      </c>
-      <c r="BE5">
-        <v>0</v>
-      </c>
-      <c r="BF5">
-        <v>0</v>
-      </c>
-      <c r="BG5">
-        <v>0</v>
-      </c>
-      <c r="BH5">
-        <v>0</v>
-      </c>
-      <c r="BI5">
-        <v>0</v>
-      </c>
-      <c r="BJ5">
-        <v>0</v>
-      </c>
-      <c r="BK5">
-        <v>0</v>
-      </c>
-      <c r="BL5">
-        <v>0</v>
-      </c>
-      <c r="BM5">
-        <v>0</v>
-      </c>
-      <c r="BN5">
-        <v>0</v>
-      </c>
-      <c r="BO5">
-        <v>0</v>
-      </c>
-      <c r="BP5">
-        <v>0</v>
-      </c>
-      <c r="BQ5">
-        <v>0</v>
-      </c>
-      <c r="BR5">
-        <v>0</v>
-      </c>
-      <c r="BS5">
-        <v>0</v>
-      </c>
-      <c r="BT5">
-        <v>0</v>
-      </c>
-      <c r="BU5">
-        <v>0</v>
-      </c>
-      <c r="BV5">
-        <v>0</v>
-      </c>
-      <c r="BW5">
-        <v>0</v>
-      </c>
-      <c r="BX5">
-        <v>0</v>
-      </c>
-      <c r="BY5">
-        <v>0</v>
+      <c r="I2" s="2">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY2" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="CA2" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CA5"/>
+    <ignoredError sqref="A1:CA2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00a272c57818f5a2598402ed9b64a3e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb7fe868ff501d2f097cc8d8c004abe7" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -1140,15 +1443,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1162,13 +1456,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{302E30A6-07D0-47DA-98EE-1574F0A3E92A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B87A842F-ABBD-4227-AC65-90A8FBB5CDE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6FBA6A7-5B2B-4104-81BE-7CAC68298164}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED0775E-7CA8-45A4-AA49-8F007F694013}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2156788C-9D3E-46C2-BACF-CE7A024B2948}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FF0A4CC-CB22-4324-AB3B-ED84433BD9BC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_764F018385AADDC0ADE7E0A24F7E0D0B11BCC454" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{157A9C2F-175C-4CAA-B67F-EB6091841A35}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_452F44925E72D3A1CE75F10E2328BE28599DF691" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62A54AC8-E9CF-428E-B127-1E0A00BE63F4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="97">
   <si>
     <t>RPRO</t>
   </si>
@@ -285,22 +285,53 @@
   </si>
   <si>
     <t>OV-007152</t>
+  </si>
+  <si>
+    <t>RPRO-250520-0832</t>
+  </si>
+  <si>
+    <t>Men's</t>
+  </si>
+  <si>
+    <t>OV-0278</t>
+  </si>
+  <si>
+    <t>11-007-M-MID (M-0149)</t>
+  </si>
+  <si>
+    <t>18-4006TPG YH-S960 EPM5 (100% Recycled PET) 44'' 198G</t>
+  </si>
+  <si>
+    <t>OV-005996</t>
+  </si>
+  <si>
+    <t>RPRO-250523-0291</t>
+  </si>
+  <si>
+    <t>Women's</t>
+  </si>
+  <si>
+    <t>OV-0270</t>
+  </si>
+  <si>
+    <t>TS-030=TS037-J (M-0097)</t>
+  </si>
+  <si>
+    <t>050-99-61(NEON) JV-A3411R Softener 44'' 240G</t>
+  </si>
+  <si>
+    <t>OV-008718</t>
+  </si>
+  <si>
+    <t>21-005-W-Low (M-0234)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -328,14 +359,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,500 +700,977 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CA2"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CA4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:79" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:79" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:79" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="CA3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:79" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="2">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2">
-        <v>2</v>
-      </c>
-      <c r="I2" s="2">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY2" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="CA2" s="2" t="s">
+      <c r="CA4" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CA2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CA1 A2:CA4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1456,7 +1958,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B87A842F-ABBD-4227-AC65-90A8FBB5CDE4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC1CC8C-1151-4000-BA35-3E131AFC8B69}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -1464,7 +1966,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED0775E-7CA8-45A4-AA49-8F007F694013}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A90EBE8-F227-41EE-B726-F065B4BE0CBF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1483,7 +1985,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FF0A4CC-CB22-4324-AB3B-ED84433BD9BC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB504156-89C5-4A53-A695-DFA724271267}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -678,727 +678,1683 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
+    <row r="2">
+      <c r="A2" t="str">
         <v>RPRO-250626-0096</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B2" t="str">
         <v>Men's</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C2" t="str">
         <v>DIE-CUT</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D2" t="str">
         <v>JV1-0695-3(arch skive)</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E2" t="str">
         <v>145-17-00 LJ-B1-1-VEPM5 44" 180G</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F2" t="str">
         <v>DC-010097</v>
       </c>
-      <c r="G11">
+      <c r="G2">
         <v>8</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <v>2</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
         <v>6</v>
       </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>0</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11">
-        <v>0</v>
-      </c>
-      <c r="BE11">
-        <v>0</v>
-      </c>
-      <c r="BF11">
-        <v>0</v>
-      </c>
-      <c r="BG11">
-        <v>0</v>
-      </c>
-      <c r="BH11">
-        <v>0</v>
-      </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>0</v>
-      </c>
-      <c r="BK11">
-        <v>0</v>
-      </c>
-      <c r="BL11">
-        <v>0</v>
-      </c>
-      <c r="BM11">
-        <v>0</v>
-      </c>
-      <c r="BN11">
-        <v>0</v>
-      </c>
-      <c r="BO11">
-        <v>0</v>
-      </c>
-      <c r="BP11">
-        <v>0</v>
-      </c>
-      <c r="BQ11">
-        <v>0</v>
-      </c>
-      <c r="BR11">
-        <v>0</v>
-      </c>
-      <c r="BS11">
-        <v>0</v>
-      </c>
-      <c r="BT11">
-        <v>0</v>
-      </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
-      <c r="BV11">
-        <v>0</v>
-      </c>
-      <c r="BW11">
-        <v>0</v>
-      </c>
-      <c r="BX11">
-        <v>0</v>
-      </c>
-      <c r="BY11">
-        <v>0</v>
-      </c>
-      <c r="BZ11">
-        <v>0</v>
-      </c>
-      <c r="CA11">
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="BZ2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
+    <row r="3">
+      <c r="A3" t="str">
         <v>RPRO-250526-0514</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B3" t="str">
         <v>Women's</v>
       </c>
-      <c r="C12" t="str">
+      <c r="C3" t="str">
         <v>OE-0198</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D3" t="str">
         <v>QD-39 (M-0502)</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E3" t="str">
         <v>71R EPM MERRY MESH(LJB-730) 44" 220G</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F3" t="str">
         <v>OE-007434</v>
       </c>
-      <c r="G12">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>0</v>
-      </c>
-      <c r="BC12">
-        <v>0</v>
-      </c>
-      <c r="BD12">
-        <v>0</v>
-      </c>
-      <c r="BE12">
-        <v>0</v>
-      </c>
-      <c r="BF12">
-        <v>0</v>
-      </c>
-      <c r="BG12">
-        <v>0</v>
-      </c>
-      <c r="BH12">
-        <v>0</v>
-      </c>
-      <c r="BI12">
-        <v>0</v>
-      </c>
-      <c r="BJ12">
-        <v>0</v>
-      </c>
-      <c r="BK12">
-        <v>0</v>
-      </c>
-      <c r="BL12">
-        <v>0</v>
-      </c>
-      <c r="BM12">
-        <v>0</v>
-      </c>
-      <c r="BN12">
-        <v>0</v>
-      </c>
-      <c r="BO12">
-        <v>0</v>
-      </c>
-      <c r="BP12">
-        <v>0</v>
-      </c>
-      <c r="BQ12">
-        <v>0</v>
-      </c>
-      <c r="BR12">
-        <v>0</v>
-      </c>
-      <c r="BS12">
-        <v>0</v>
-      </c>
-      <c r="BT12">
-        <v>0</v>
-      </c>
-      <c r="BU12">
-        <v>0</v>
-      </c>
-      <c r="BV12">
-        <v>0</v>
-      </c>
-      <c r="BW12">
-        <v>0</v>
-      </c>
-      <c r="BX12">
-        <v>0</v>
-      </c>
-      <c r="BY12">
-        <v>0</v>
-      </c>
-      <c r="BZ12">
-        <v>0</v>
-      </c>
-      <c r="CA12">
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
+    <row r="4">
+      <c r="A4" t="str">
         <v>RPRO-250610-0389</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B4" t="str">
         <v>Men's</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C4" t="str">
         <v>OV-0256</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D4" t="str">
         <v>21-005-M-Low (M-0235)</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E4" t="str">
         <v>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F4" t="str">
         <v>OV-008378</v>
       </c>
-      <c r="G13">
+      <c r="G4">
         <v>26</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>1</v>
       </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
         <v>25</v>
       </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>0</v>
-      </c>
-      <c r="BC13">
-        <v>0</v>
-      </c>
-      <c r="BD13">
-        <v>0</v>
-      </c>
-      <c r="BE13">
-        <v>0</v>
-      </c>
-      <c r="BF13">
-        <v>0</v>
-      </c>
-      <c r="BG13">
-        <v>0</v>
-      </c>
-      <c r="BH13">
-        <v>0</v>
-      </c>
-      <c r="BI13">
-        <v>0</v>
-      </c>
-      <c r="BJ13">
-        <v>0</v>
-      </c>
-      <c r="BK13">
-        <v>0</v>
-      </c>
-      <c r="BL13">
-        <v>0</v>
-      </c>
-      <c r="BM13">
-        <v>0</v>
-      </c>
-      <c r="BN13">
-        <v>0</v>
-      </c>
-      <c r="BO13">
-        <v>0</v>
-      </c>
-      <c r="BP13">
-        <v>0</v>
-      </c>
-      <c r="BQ13">
-        <v>0</v>
-      </c>
-      <c r="BR13">
-        <v>0</v>
-      </c>
-      <c r="BS13">
-        <v>0</v>
-      </c>
-      <c r="BT13">
-        <v>0</v>
-      </c>
-      <c r="BU13">
-        <v>0</v>
-      </c>
-      <c r="BV13">
-        <v>0</v>
-      </c>
-      <c r="BW13">
-        <v>0</v>
-      </c>
-      <c r="BX13">
-        <v>0</v>
-      </c>
-      <c r="BY13">
-        <v>0</v>
-      </c>
-      <c r="BZ13">
-        <v>0</v>
-      </c>
-      <c r="CA13">
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>RPRO-250626-0096</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Men's</v>
+      </c>
+      <c r="C5" t="str">
+        <v>DIE-CUT</v>
+      </c>
+      <c r="D5" t="str">
+        <v>JV1-0695-3(arch skive)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>145-17-00 LJ-B1-1-VEPM5 44" 180G</v>
+      </c>
+      <c r="F5" t="str">
+        <v>DC-010097</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>6</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>RPRO-250526-0514</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Women's</v>
+      </c>
+      <c r="C6" t="str">
+        <v>OE-0198</v>
+      </c>
+      <c r="D6" t="str">
+        <v>QD-39 (M-0502)</v>
+      </c>
+      <c r="E6" t="str">
+        <v>71R EPM MERRY MESH(LJB-730) 44" 220G</v>
+      </c>
+      <c r="F6" t="str">
+        <v>OE-007434</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>RPRO-250610-0389</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Men's</v>
+      </c>
+      <c r="C7" t="str">
+        <v>OV-0256</v>
+      </c>
+      <c r="D7" t="str">
+        <v>21-005-M-Low (M-0235)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
+      </c>
+      <c r="F7" t="str">
+        <v>OV-008378</v>
+      </c>
+      <c r="G7">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>25</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>RPRO-250606-0428</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Men's</v>
+      </c>
+      <c r="C8" t="str">
+        <v>OV-0256</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ON-112 (M-0236)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
+      </c>
+      <c r="F8" t="str">
+        <v>OV-008350</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CB14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CB9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1686,13 +2642,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{833D3F70-819B-4B7A-BC0B-55813A3880F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A2EC36-4C36-4AC4-A4F8-8D5724A706EE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E3638D8-8726-45D2-894B-2C68FA3DC399}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1649B39-C370-4C94-87EB-4139FE1E2547}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DC8FD4E-43C5-47A4-AC46-9F2D906C87FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91A25EBB-2661-42F5-8DC2-FCDD4898E9C0}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,260 +421,263 @@
       <c r="G1" t="str">
         <v>TOTAL</v>
       </c>
-      <c r="H1">
+      <c r="H1" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="I1">
         <v>1</v>
-      </c>
-      <c r="I1">
-        <f>H1+0.5</f>
-        <v>1.5</v>
       </c>
       <c r="J1">
         <f>I1+0.5</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K1">
         <f>J1+0.5</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L1">
         <f>K1+0.5</f>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M1">
         <f>L1+0.5</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N1">
         <f>M1+0.5</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O1">
         <f>N1+0.5</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P1">
         <f>O1+0.5</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q1">
         <f>P1+0.5</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R1">
         <f>Q1+0.5</f>
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="S1">
         <f>R1+0.5</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="T1">
         <f>S1+0.5</f>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="U1">
         <f>T1+0.5</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="V1">
         <f>U1+0.5</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W1">
         <f>V1+0.5</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="X1">
         <f>W1+0.5</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Y1">
         <f>X1+0.5</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z1">
         <f>Y1+0.5</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AA1">
         <f>Z1+0.5</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB1">
         <f>AA1+0.5</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC1">
         <f>AB1+0.5</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD1">
         <f>AC1+0.5</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE1">
         <f>AD1+0.5</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AF1">
         <f>AE1+0.5</f>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG1">
         <f>AF1+0.5</f>
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH1">
         <f>AG1+0.5</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI1">
         <f>AH1+0.5</f>
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AJ1">
         <f>AI1+0.5</f>
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK1">
         <f>AJ1+0.5</f>
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL1">
         <f>AK1+0.5</f>
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AM1">
         <f>AL1+0.5</f>
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AN1">
         <f>AM1+0.5</f>
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO1">
         <f>AN1+0.5</f>
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP1">
         <f>AO1+0.5</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ1">
         <f>AP1+0.5</f>
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR1">
         <f>AQ1+0.5</f>
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS1">
         <f>AR1+0.5</f>
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT1">
         <f>AS1+0.5</f>
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU1">
         <f>AT1+0.5</f>
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="AV1">
         <f>AU1+0.5</f>
+        <v>20.5</v>
+      </c>
+      <c r="AW1">
+        <f>AV1+0.5</f>
         <v>21</v>
       </c>
-      <c r="AW1">
+      <c r="AX1">
         <v>22</v>
       </c>
-      <c r="AX1">
+      <c r="AY1">
         <v>23</v>
       </c>
-      <c r="AY1">
+      <c r="AZ1">
         <v>24</v>
       </c>
-      <c r="AZ1">
+      <c r="BA1">
         <v>25</v>
       </c>
-      <c r="BA1">
+      <c r="BB1">
         <v>26</v>
       </c>
-      <c r="BB1">
+      <c r="BC1">
         <v>27</v>
       </c>
-      <c r="BC1">
+      <c r="BD1">
         <v>28</v>
       </c>
-      <c r="BD1">
+      <c r="BE1">
         <v>29</v>
       </c>
-      <c r="BE1">
+      <c r="BF1">
         <v>30</v>
       </c>
-      <c r="BF1">
+      <c r="BG1">
         <v>31</v>
       </c>
-      <c r="BG1">
+      <c r="BH1">
         <v>32</v>
       </c>
-      <c r="BH1">
+      <c r="BI1">
         <v>33</v>
       </c>
-      <c r="BI1">
+      <c r="BJ1">
         <v>34</v>
       </c>
-      <c r="BJ1">
+      <c r="BK1">
         <v>35</v>
       </c>
-      <c r="BK1">
+      <c r="BL1">
         <v>36</v>
       </c>
-      <c r="BL1">
+      <c r="BM1">
         <v>37</v>
       </c>
-      <c r="BM1">
+      <c r="BN1">
         <v>38</v>
       </c>
-      <c r="BN1">
+      <c r="BO1">
         <v>39</v>
       </c>
-      <c r="BO1">
+      <c r="BP1">
         <v>40</v>
       </c>
-      <c r="BP1">
+      <c r="BQ1">
         <v>41</v>
       </c>
-      <c r="BQ1">
+      <c r="BR1">
         <v>42</v>
       </c>
-      <c r="BR1">
+      <c r="BS1">
         <v>43</v>
       </c>
-      <c r="BS1">
+      <c r="BT1">
         <v>44</v>
       </c>
-      <c r="BT1">
+      <c r="BU1">
         <v>45</v>
       </c>
-      <c r="BU1">
+      <c r="BV1">
         <v>46</v>
       </c>
-      <c r="BV1">
+      <c r="BW1">
         <v>47</v>
       </c>
-      <c r="BW1">
+      <c r="BX1">
         <v>48</v>
       </c>
-      <c r="BX1">
+      <c r="BY1">
         <v>49</v>
       </c>
-      <c r="BY1">
+      <c r="BZ1">
         <v>50</v>
       </c>
-      <c r="BZ1">
-        <v>0</v>
-      </c>
       <c r="CA1">
+        <v>0</v>
+      </c>
+      <c r="CB1">
         <v>0</v>
       </c>
     </row>
@@ -698,7 +701,7 @@
         <v>DC-010097</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -734,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -746,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -1397,25 +1400,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>RPRO-250626-0096</v>
+        <v>RPRO-250606-0428</v>
       </c>
       <c r="B5" t="str">
         <v>Men's</v>
       </c>
       <c r="C5" t="str">
-        <v>DIE-CUT</v>
+        <v>OV-0256</v>
       </c>
       <c r="D5" t="str">
-        <v>JV1-0695-3(arch skive)</v>
+        <v>ON-112 (M-0236)</v>
       </c>
       <c r="E5" t="str">
-        <v>145-17-00 LJ-B1-1-VEPM5 44" 180G</v>
+        <v>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
       </c>
       <c r="F5" t="str">
-        <v>DC-010097</v>
+        <v>OV-008350</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1451,19 +1454,19 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5">
         <v>0</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1631,730 +1634,13 @@
         <v>0</v>
       </c>
       <c r="CA5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>RPRO-250526-0514</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Women's</v>
-      </c>
-      <c r="C6" t="str">
-        <v>OE-0198</v>
-      </c>
-      <c r="D6" t="str">
-        <v>QD-39 (M-0502)</v>
-      </c>
-      <c r="E6" t="str">
-        <v>71R EPM MERRY MESH(LJB-730) 44" 220G</v>
-      </c>
-      <c r="F6" t="str">
-        <v>OE-007434</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6">
-        <v>0</v>
-      </c>
-      <c r="BE6">
-        <v>0</v>
-      </c>
-      <c r="BF6">
-        <v>0</v>
-      </c>
-      <c r="BG6">
-        <v>0</v>
-      </c>
-      <c r="BH6">
-        <v>0</v>
-      </c>
-      <c r="BI6">
-        <v>0</v>
-      </c>
-      <c r="BJ6">
-        <v>0</v>
-      </c>
-      <c r="BK6">
-        <v>0</v>
-      </c>
-      <c r="BL6">
-        <v>0</v>
-      </c>
-      <c r="BM6">
-        <v>0</v>
-      </c>
-      <c r="BN6">
-        <v>0</v>
-      </c>
-      <c r="BO6">
-        <v>0</v>
-      </c>
-      <c r="BP6">
-        <v>0</v>
-      </c>
-      <c r="BQ6">
-        <v>0</v>
-      </c>
-      <c r="BR6">
-        <v>0</v>
-      </c>
-      <c r="BS6">
-        <v>0</v>
-      </c>
-      <c r="BT6">
-        <v>0</v>
-      </c>
-      <c r="BU6">
-        <v>0</v>
-      </c>
-      <c r="BV6">
-        <v>0</v>
-      </c>
-      <c r="BW6">
-        <v>0</v>
-      </c>
-      <c r="BX6">
-        <v>0</v>
-      </c>
-      <c r="BY6">
-        <v>0</v>
-      </c>
-      <c r="BZ6">
-        <v>0</v>
-      </c>
-      <c r="CA6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>RPRO-250610-0389</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C7" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D7" t="str">
-        <v>21-005-M-Low (M-0235)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F7" t="str">
-        <v>OV-008378</v>
-      </c>
-      <c r="G7">
-        <v>26</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>25</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7">
-        <v>0</v>
-      </c>
-      <c r="BE7">
-        <v>0</v>
-      </c>
-      <c r="BF7">
-        <v>0</v>
-      </c>
-      <c r="BG7">
-        <v>0</v>
-      </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>0</v>
-      </c>
-      <c r="BJ7">
-        <v>0</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7">
-        <v>0</v>
-      </c>
-      <c r="BM7">
-        <v>0</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7">
-        <v>0</v>
-      </c>
-      <c r="BP7">
-        <v>0</v>
-      </c>
-      <c r="BQ7">
-        <v>0</v>
-      </c>
-      <c r="BR7">
-        <v>0</v>
-      </c>
-      <c r="BS7">
-        <v>0</v>
-      </c>
-      <c r="BT7">
-        <v>0</v>
-      </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
-      <c r="BV7">
-        <v>0</v>
-      </c>
-      <c r="BW7">
-        <v>0</v>
-      </c>
-      <c r="BX7">
-        <v>0</v>
-      </c>
-      <c r="BY7">
-        <v>0</v>
-      </c>
-      <c r="BZ7">
-        <v>0</v>
-      </c>
-      <c r="CA7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>RPRO-250606-0428</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C8" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D8" t="str">
-        <v>ON-112 (M-0236)</v>
-      </c>
-      <c r="E8" t="str">
-        <v>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F8" t="str">
-        <v>OV-008350</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>3</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>0</v>
-      </c>
-      <c r="BC8">
-        <v>0</v>
-      </c>
-      <c r="BD8">
-        <v>0</v>
-      </c>
-      <c r="BE8">
-        <v>0</v>
-      </c>
-      <c r="BF8">
-        <v>0</v>
-      </c>
-      <c r="BG8">
-        <v>0</v>
-      </c>
-      <c r="BH8">
-        <v>0</v>
-      </c>
-      <c r="BI8">
-        <v>0</v>
-      </c>
-      <c r="BJ8">
-        <v>0</v>
-      </c>
-      <c r="BK8">
-        <v>0</v>
-      </c>
-      <c r="BL8">
-        <v>0</v>
-      </c>
-      <c r="BM8">
-        <v>0</v>
-      </c>
-      <c r="BN8">
-        <v>0</v>
-      </c>
-      <c r="BO8">
-        <v>0</v>
-      </c>
-      <c r="BP8">
-        <v>0</v>
-      </c>
-      <c r="BQ8">
-        <v>0</v>
-      </c>
-      <c r="BR8">
-        <v>0</v>
-      </c>
-      <c r="BS8">
-        <v>0</v>
-      </c>
-      <c r="BT8">
-        <v>0</v>
-      </c>
-      <c r="BU8">
-        <v>0</v>
-      </c>
-      <c r="BV8">
-        <v>0</v>
-      </c>
-      <c r="BW8">
-        <v>0</v>
-      </c>
-      <c r="BX8">
-        <v>0</v>
-      </c>
-      <c r="BY8">
-        <v>0</v>
-      </c>
-      <c r="BZ8">
-        <v>0</v>
-      </c>
-      <c r="CA8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CB9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CB6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2642,13 +1928,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A2EC36-4C36-4AC4-A4F8-8D5724A706EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFA190E4-0FC4-40F2-92AD-2DA43CDDC4B0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1649B39-C370-4C94-87EB-4139FE1E2547}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60B096C9-2FBE-4D9A-B86D-7BF7FB454154}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91A25EBB-2661-42F5-8DC2-FCDD4898E9C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB276B2-798A-44FF-BEBD-D89F4E355E1A}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -1,41 +1,144 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_602794818082BA50B1AB938F59E73FCC41880EC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{546D237A-E8A8-4F15-B994-AD4A350F1DF2}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Supplement" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+  <si>
+    <t>RPRO</t>
+  </si>
+  <si>
+    <t>Giới tính</t>
+  </si>
+  <si>
+    <t>Mã khuôn</t>
+  </si>
+  <si>
+    <t>Mã dao</t>
+  </si>
+  <si>
+    <t>Vải</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>RPRO-250626-0096</t>
+  </si>
+  <si>
+    <t>Men's</t>
+  </si>
+  <si>
+    <t>DIE-CUT</t>
+  </si>
+  <si>
+    <t>JV1-0695-3(arch skive)</t>
+  </si>
+  <si>
+    <t>145-17-00 LJ-B1-1-VEPM5 44" 180G</t>
+  </si>
+  <si>
+    <t>DC-010097</t>
+  </si>
+  <si>
+    <t>2025-07-23T06:25:54.592712+00:00</t>
+  </si>
+  <si>
+    <t>RPRO-250526-0514</t>
+  </si>
+  <si>
+    <t>Women's</t>
+  </si>
+  <si>
+    <t>OE-0198</t>
+  </si>
+  <si>
+    <t>QD-39 (M-0502)</t>
+  </si>
+  <si>
+    <t>71R EPM MERRY MESH(LJB-730) 44" 220G</t>
+  </si>
+  <si>
+    <t>OE-007434</t>
+  </si>
+  <si>
+    <t>2025-07-23T07:24:36.736422+00:00</t>
+  </si>
+  <si>
+    <t>RPRO-250610-0389</t>
+  </si>
+  <si>
+    <t>OV-0256</t>
+  </si>
+  <si>
+    <t>21-005-M-Low (M-0235)</t>
+  </si>
+  <si>
+    <t>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-008378</t>
+  </si>
+  <si>
+    <t>2025-07-23T09:19:54.285537+00:00</t>
+  </si>
+  <si>
+    <t>RPRO-250606-0428</t>
+  </si>
+  <si>
+    <t>ON-112 (M-0236)</t>
+  </si>
+  <si>
+    <t>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-008350</t>
+  </si>
+  <si>
+    <t>2025-07-23T15:26:03.594943+00:00</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +168,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,195 +507,200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:CB5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="30.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>RPRO</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Giới tính</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Mã khuôn</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Mã dao</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Vải</v>
-      </c>
-      <c r="F1" t="str">
-        <v>BOM</v>
-      </c>
-      <c r="G1" t="str">
-        <v>TOTAL</v>
-      </c>
-      <c r="H1" t="str">
-        <v>created_at</v>
+    <row r="1" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
       <c r="I1">
         <v>1</v>
       </c>
       <c r="J1">
-        <f>I1+0.5</f>
+        <f t="shared" ref="J1:AW1" si="0">I1+0.5</f>
         <v>1.5</v>
       </c>
       <c r="K1">
-        <f>J1+0.5</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="L1">
-        <f>K1+0.5</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="M1">
-        <f>L1+0.5</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N1">
-        <f>M1+0.5</f>
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
       <c r="O1">
-        <f>N1+0.5</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="P1">
-        <f>O1+0.5</f>
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
       <c r="Q1">
-        <f>P1+0.5</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="R1">
-        <f>Q1+0.5</f>
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
       <c r="S1">
-        <f>R1+0.5</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="T1">
-        <f>S1+0.5</f>
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
       <c r="U1">
-        <f>T1+0.5</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="V1">
-        <f>U1+0.5</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="W1">
-        <f>V1+0.5</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="X1">
-        <f>W1+0.5</f>
+        <f t="shared" si="0"/>
         <v>8.5</v>
       </c>
       <c r="Y1">
-        <f>X1+0.5</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="Z1">
-        <f>Y1+0.5</f>
+        <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
       <c r="AA1">
-        <f>Z1+0.5</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="AB1">
-        <f>AA1+0.5</f>
+        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="AC1">
-        <f>AB1+0.5</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="AD1">
-        <f>AC1+0.5</f>
+        <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
       <c r="AE1">
-        <f>AD1+0.5</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="AF1">
-        <f>AE1+0.5</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
       <c r="AG1">
-        <f>AF1+0.5</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="AH1">
-        <f>AG1+0.5</f>
+        <f t="shared" si="0"/>
         <v>13.5</v>
       </c>
       <c r="AI1">
-        <f>AH1+0.5</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="AJ1">
-        <f>AI1+0.5</f>
+        <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
       <c r="AK1">
-        <f>AJ1+0.5</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="AL1">
-        <f>AK1+0.5</f>
+        <f t="shared" si="0"/>
         <v>15.5</v>
       </c>
       <c r="AM1">
-        <f>AL1+0.5</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="AN1">
-        <f>AM1+0.5</f>
+        <f t="shared" si="0"/>
         <v>16.5</v>
       </c>
       <c r="AO1">
-        <f>AN1+0.5</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="AP1">
-        <f>AO1+0.5</f>
+        <f t="shared" si="0"/>
         <v>17.5</v>
       </c>
       <c r="AQ1">
-        <f>AP1+0.5</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="AR1">
-        <f>AQ1+0.5</f>
+        <f t="shared" si="0"/>
         <v>18.5</v>
       </c>
       <c r="AS1">
-        <f>AR1+0.5</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="AT1">
-        <f>AS1+0.5</f>
+        <f t="shared" si="0"/>
         <v>19.5</v>
       </c>
       <c r="AU1">
-        <f>AT1+0.5</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="AV1">
-        <f>AU1+0.5</f>
+        <f t="shared" si="0"/>
         <v>20.5</v>
       </c>
       <c r="AW1">
-        <f>AV1+0.5</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="AX1">
@@ -681,30 +797,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>RPRO-250626-0096</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C2" t="str">
-        <v>DIE-CUT</v>
-      </c>
-      <c r="D2" t="str">
-        <v>JV1-0695-3(arch skive)</v>
-      </c>
-      <c r="E2" t="str">
-        <v>145-17-00 LJ-B1-1-VEPM5 44" 180G</v>
-      </c>
-      <c r="F2" t="str">
-        <v>DC-010097</v>
+    <row r="2" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
-      <c r="H2">
-        <v>0</v>
+      <c r="H2" t="s">
+        <v>14</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -737,11 +853,11 @@
         <v>0</v>
       </c>
       <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
         <v>3</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
         <v>0</v>
       </c>
@@ -749,11 +865,11 @@
         <v>0</v>
       </c>
       <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
         <v>7</v>
       </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
       <c r="Y2">
         <v>0</v>
       </c>
@@ -919,31 +1035,34 @@
       <c r="CA2">
         <v>0</v>
       </c>
+      <c r="CB2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>RPRO-250526-0514</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Women's</v>
-      </c>
-      <c r="C3" t="str">
-        <v>OE-0198</v>
-      </c>
-      <c r="D3" t="str">
-        <v>QD-39 (M-0502)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>71R EPM MERRY MESH(LJB-730) 44" 220G</v>
-      </c>
-      <c r="F3" t="str">
-        <v>OE-007434</v>
+    <row r="3" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>0</v>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -973,11 +1092,11 @@
         <v>0</v>
       </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>1</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
       <c r="T3">
         <v>0</v>
       </c>
@@ -1158,31 +1277,34 @@
       <c r="CA3">
         <v>0</v>
       </c>
+      <c r="CB3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>RPRO-250610-0389</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C4" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D4" t="str">
-        <v>21-005-M-Low (M-0235)</v>
-      </c>
-      <c r="E4" t="str">
-        <v>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F4" t="str">
-        <v>OV-008378</v>
+    <row r="4" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
       </c>
       <c r="G4">
         <v>26</v>
       </c>
-      <c r="H4">
-        <v>0</v>
+      <c r="H4" t="s">
+        <v>27</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1218,20 +1340,20 @@
         <v>0</v>
       </c>
       <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>1</v>
       </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
         <v>25</v>
       </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
       <c r="Y4">
         <v>0</v>
       </c>
@@ -1397,31 +1519,34 @@
       <c r="CA4">
         <v>0</v>
       </c>
+      <c r="CB4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>RPRO-250606-0428</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C5" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D5" t="str">
-        <v>ON-112 (M-0236)</v>
-      </c>
-      <c r="E5" t="str">
-        <v>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F5" t="str">
-        <v>OV-008350</v>
+    <row r="5" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5">
-        <v>0</v>
+      <c r="H5" t="s">
+        <v>32</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1457,17 +1582,17 @@
         <v>0</v>
       </c>
       <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>1</v>
       </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
       <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
         <v>3</v>
       </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
       <c r="X5">
         <v>0</v>
       </c>
@@ -1634,13 +1759,16 @@
         <v>0</v>
       </c>
       <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CB6"/>
+    <ignoredError sqref="A1:CB6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1928,13 +2056,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFA190E4-0FC4-40F2-92AD-2DA43CDDC4B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1203F6-C7DD-46DD-B04D-465C62CE5993}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60B096C9-2FBE-4D9A-B86D-7BF7FB454154}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB03B1FD-ACA5-4160-9045-26DC33F4F8F4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB276B2-798A-44FF-BEBD-D89F4E355E1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006110E2-C902-4485-9F6A-AA41EBB6F6F4}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -2056,13 +2056,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC1203F6-C7DD-46DD-B04D-465C62CE5993}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F31B56E8-F284-42EB-83C1-177BF242A282}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB03B1FD-ACA5-4160-9045-26DC33F4F8F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{374A4FF6-6D4A-4D9E-A4D3-F2803F6EADF9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006110E2-C902-4485-9F6A-AA41EBB6F6F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{492DA096-41B2-41EE-B99E-A0CDAB99C2C0}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_602794818082BA50B1AB938F59E73FCC41880EC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{546D237A-E8A8-4F15-B994-AD4A350F1DF2}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_43CF8293CFDA528EC6B4FD45B31F8D91119FF501" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{606414E1-6EDA-488C-A7F1-7E4226E794C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
     <t>DC-010097</t>
   </si>
   <si>
-    <t>2025-07-23T06:25:54.592712+00:00</t>
+    <t>20:25:54 23/7/2025</t>
   </si>
   <si>
     <t>RPRO-250526-0514</t>
@@ -98,7 +98,7 @@
     <t>OE-007434</t>
   </si>
   <si>
-    <t>2025-07-23T07:24:36.736422+00:00</t>
+    <t>21:24:36 23/7/2025</t>
   </si>
   <si>
     <t>RPRO-250610-0389</t>
@@ -116,7 +116,7 @@
     <t>OV-008378</t>
   </si>
   <si>
-    <t>2025-07-23T09:19:54.285537+00:00</t>
+    <t>23:19:54 23/7/2025</t>
   </si>
   <si>
     <t>RPRO-250606-0428</t>
@@ -131,7 +131,7 @@
     <t>OV-008350</t>
   </si>
   <si>
-    <t>2025-07-23T15:26:03.594943+00:00</t>
+    <t>05:26:03 24/7/2025</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
   <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="30.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
@@ -1774,6 +1774,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00a272c57818f5a2598402ed9b64a3e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb7fe868ff501d2f097cc8d8c004abe7" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -2034,35 +2055,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F31B56E8-F284-42EB-83C1-177BF242A282}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD4B7915-6F14-43C4-9C3D-3C793CC93AF4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{374A4FF6-6D4A-4D9E-A4D3-F2803F6EADF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E908637C-941A-4B6A-B2CE-829FCB14F22B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{492DA096-41B2-41EE-B99E-A0CDAB99C2C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FD1278-F692-4F72-A2D4-540DE266848F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_43CF8293CFDA528EC6B4FD45B31F8D91119FF501" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{606414E1-6EDA-488C-A7F1-7E4226E794C4}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_602794818082BA50B14B1597B5E1379441883697" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845201F2-26E3-4AA7-BE88-805CB2DBA710}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>RPRO</t>
   </si>
@@ -132,6 +132,21 @@
   </si>
   <si>
     <t>05:26:03 24/7/2025</t>
+  </si>
+  <si>
+    <t>RPRO-250627-0145</t>
+  </si>
+  <si>
+    <t>QA-7H (D-0256) (skive arch)</t>
+  </si>
+  <si>
+    <t>10A (PP)LINING KNIT MATTE MICRO (HOOD) REC 44" 250G</t>
+  </si>
+  <si>
+    <t>DC-011263</t>
+  </si>
+  <si>
+    <t>05:58:44 24/7/2025</t>
   </si>
 </sst>
 </file>
@@ -509,9 +524,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -817,7 +833,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -856,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -1765,36 +1781,257 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CB6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CB7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00a272c57818f5a2598402ed9b64a3e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb7fe868ff501d2f097cc8d8c004abe7" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
@@ -2055,40 +2292,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="71b44b8b-5734-40bc-bcd6-983774da7c1c" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD4B7915-6F14-43C4-9C3D-3C793CC93AF4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F584F6D1-7DD2-4AB3-8D49-E584EC6D383B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E908637C-941A-4B6A-B2CE-829FCB14F22B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7594A01-2DF5-4686-85FE-9DB508406BE9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FD1278-F692-4F72-A2D4-540DE266848F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD4BDA8F-0C11-44C1-9E2E-E3DD1647FF1B}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -2314,13 +2314,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F584F6D1-7DD2-4AB3-8D49-E584EC6D383B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DC4A862-CA12-4D99-894E-E8459D684E1F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7594A01-2DF5-4686-85FE-9DB508406BE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBAFA2E0-45AD-4B3E-9CAC-6AE4A1C39391}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD4BDA8F-0C11-44C1-9E2E-E3DD1647FF1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F70E2-34E6-440D-83B6-CF70E762958C}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_602794818082BA50B14B1597B5E1379441883697" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845201F2-26E3-4AA7-BE88-805CB2DBA710}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_790745963FFAD3847277F4C2D36D9BE9345EFA16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C978D78B-4CF1-497C-90D9-E86371E10B68}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,11 +523,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2293,15 +2291,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
@@ -2313,14 +2302,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DC4A862-CA12-4D99-894E-E8459D684E1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319190FD-FD72-4751-8599-FDB1FF03ABA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBAFA2E0-45AD-4B3E-9CAC-6AE4A1C39391}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1CBB147-C6F6-4698-AFA8-62992EEFE699}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
+    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34F70E2-34E6-440D-83B6-CF70E762958C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48D00D19-7C52-46C6-8D43-E417AB68CFB6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_790745963FFAD3847277F4C2D36D9BE9345EFA16" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C978D78B-4CF1-497C-90D9-E86371E10B68}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_8E1F44B0599B5389FE26624A271CB3BF095CFE13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13727F7D-4F34-4BDB-98EA-DF82AA16C451}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>RPRO</t>
   </si>
@@ -59,81 +59,12 @@
     <t>created_at</t>
   </si>
   <si>
-    <t>RPRO-250626-0096</t>
-  </si>
-  <si>
-    <t>Men's</t>
-  </si>
-  <si>
     <t>DIE-CUT</t>
   </si>
   <si>
-    <t>JV1-0695-3(arch skive)</t>
-  </si>
-  <si>
-    <t>145-17-00 LJ-B1-1-VEPM5 44" 180G</t>
-  </si>
-  <si>
-    <t>DC-010097</t>
-  </si>
-  <si>
-    <t>20:25:54 23/7/2025</t>
-  </si>
-  <si>
-    <t>RPRO-250526-0514</t>
-  </si>
-  <si>
     <t>Women's</t>
   </si>
   <si>
-    <t>OE-0198</t>
-  </si>
-  <si>
-    <t>QD-39 (M-0502)</t>
-  </si>
-  <si>
-    <t>71R EPM MERRY MESH(LJB-730) 44" 220G</t>
-  </si>
-  <si>
-    <t>OE-007434</t>
-  </si>
-  <si>
-    <t>21:24:36 23/7/2025</t>
-  </si>
-  <si>
-    <t>RPRO-250610-0389</t>
-  </si>
-  <si>
-    <t>OV-0256</t>
-  </si>
-  <si>
-    <t>21-005-M-Low (M-0235)</t>
-  </si>
-  <si>
-    <t>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
-  </si>
-  <si>
-    <t>OV-008378</t>
-  </si>
-  <si>
-    <t>23:19:54 23/7/2025</t>
-  </si>
-  <si>
-    <t>RPRO-250606-0428</t>
-  </si>
-  <si>
-    <t>ON-112 (M-0236)</t>
-  </si>
-  <si>
-    <t>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
-  </si>
-  <si>
-    <t>OV-008350</t>
-  </si>
-  <si>
-    <t>05:26:03 24/7/2025</t>
-  </si>
-  <si>
     <t>RPRO-250627-0145</t>
   </si>
   <si>
@@ -146,7 +77,7 @@
     <t>DC-011263</t>
   </si>
   <si>
-    <t>05:58:44 24/7/2025</t>
+    <t>24/07/2025 05:58:44</t>
   </si>
 </sst>
 </file>
@@ -523,10 +454,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
@@ -813,13 +744,13 @@
     </row>
     <row r="2" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -831,7 +762,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -870,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -882,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y2">
         <v>0</v>
@@ -1050,981 +981,13 @@
         <v>0</v>
       </c>
       <c r="CB2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>0</v>
-      </c>
-      <c r="BC3">
-        <v>0</v>
-      </c>
-      <c r="BD3">
-        <v>0</v>
-      </c>
-      <c r="BE3">
-        <v>0</v>
-      </c>
-      <c r="BF3">
-        <v>0</v>
-      </c>
-      <c r="BG3">
-        <v>0</v>
-      </c>
-      <c r="BH3">
-        <v>0</v>
-      </c>
-      <c r="BI3">
-        <v>0</v>
-      </c>
-      <c r="BJ3">
-        <v>0</v>
-      </c>
-      <c r="BK3">
-        <v>0</v>
-      </c>
-      <c r="BL3">
-        <v>0</v>
-      </c>
-      <c r="BM3">
-        <v>0</v>
-      </c>
-      <c r="BN3">
-        <v>0</v>
-      </c>
-      <c r="BO3">
-        <v>0</v>
-      </c>
-      <c r="BP3">
-        <v>0</v>
-      </c>
-      <c r="BQ3">
-        <v>0</v>
-      </c>
-      <c r="BR3">
-        <v>0</v>
-      </c>
-      <c r="BS3">
-        <v>0</v>
-      </c>
-      <c r="BT3">
-        <v>0</v>
-      </c>
-      <c r="BU3">
-        <v>0</v>
-      </c>
-      <c r="BV3">
-        <v>0</v>
-      </c>
-      <c r="BW3">
-        <v>0</v>
-      </c>
-      <c r="BX3">
-        <v>0</v>
-      </c>
-      <c r="BY3">
-        <v>0</v>
-      </c>
-      <c r="BZ3">
-        <v>0</v>
-      </c>
-      <c r="CA3">
-        <v>0</v>
-      </c>
-      <c r="CB3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>25</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
-      <c r="BC4">
-        <v>0</v>
-      </c>
-      <c r="BD4">
-        <v>0</v>
-      </c>
-      <c r="BE4">
-        <v>0</v>
-      </c>
-      <c r="BF4">
-        <v>0</v>
-      </c>
-      <c r="BG4">
-        <v>0</v>
-      </c>
-      <c r="BH4">
-        <v>0</v>
-      </c>
-      <c r="BI4">
-        <v>0</v>
-      </c>
-      <c r="BJ4">
-        <v>0</v>
-      </c>
-      <c r="BK4">
-        <v>0</v>
-      </c>
-      <c r="BL4">
-        <v>0</v>
-      </c>
-      <c r="BM4">
-        <v>0</v>
-      </c>
-      <c r="BN4">
-        <v>0</v>
-      </c>
-      <c r="BO4">
-        <v>0</v>
-      </c>
-      <c r="BP4">
-        <v>0</v>
-      </c>
-      <c r="BQ4">
-        <v>0</v>
-      </c>
-      <c r="BR4">
-        <v>0</v>
-      </c>
-      <c r="BS4">
-        <v>0</v>
-      </c>
-      <c r="BT4">
-        <v>0</v>
-      </c>
-      <c r="BU4">
-        <v>0</v>
-      </c>
-      <c r="BV4">
-        <v>0</v>
-      </c>
-      <c r="BW4">
-        <v>0</v>
-      </c>
-      <c r="BX4">
-        <v>0</v>
-      </c>
-      <c r="BY4">
-        <v>0</v>
-      </c>
-      <c r="BZ4">
-        <v>0</v>
-      </c>
-      <c r="CA4">
-        <v>0</v>
-      </c>
-      <c r="CB4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>3</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5">
-        <v>0</v>
-      </c>
-      <c r="BE5">
-        <v>0</v>
-      </c>
-      <c r="BF5">
-        <v>0</v>
-      </c>
-      <c r="BG5">
-        <v>0</v>
-      </c>
-      <c r="BH5">
-        <v>0</v>
-      </c>
-      <c r="BI5">
-        <v>0</v>
-      </c>
-      <c r="BJ5">
-        <v>0</v>
-      </c>
-      <c r="BK5">
-        <v>0</v>
-      </c>
-      <c r="BL5">
-        <v>0</v>
-      </c>
-      <c r="BM5">
-        <v>0</v>
-      </c>
-      <c r="BN5">
-        <v>0</v>
-      </c>
-      <c r="BO5">
-        <v>0</v>
-      </c>
-      <c r="BP5">
-        <v>0</v>
-      </c>
-      <c r="BQ5">
-        <v>0</v>
-      </c>
-      <c r="BR5">
-        <v>0</v>
-      </c>
-      <c r="BS5">
-        <v>0</v>
-      </c>
-      <c r="BT5">
-        <v>0</v>
-      </c>
-      <c r="BU5">
-        <v>0</v>
-      </c>
-      <c r="BV5">
-        <v>0</v>
-      </c>
-      <c r="BW5">
-        <v>0</v>
-      </c>
-      <c r="BX5">
-        <v>0</v>
-      </c>
-      <c r="BY5">
-        <v>0</v>
-      </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>2</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6">
-        <v>0</v>
-      </c>
-      <c r="BE6">
-        <v>0</v>
-      </c>
-      <c r="BF6">
-        <v>0</v>
-      </c>
-      <c r="BG6">
-        <v>0</v>
-      </c>
-      <c r="BH6">
-        <v>0</v>
-      </c>
-      <c r="BI6">
-        <v>0</v>
-      </c>
-      <c r="BJ6">
-        <v>0</v>
-      </c>
-      <c r="BK6">
-        <v>0</v>
-      </c>
-      <c r="BL6">
-        <v>0</v>
-      </c>
-      <c r="BM6">
-        <v>0</v>
-      </c>
-      <c r="BN6">
-        <v>0</v>
-      </c>
-      <c r="BO6">
-        <v>0</v>
-      </c>
-      <c r="BP6">
-        <v>0</v>
-      </c>
-      <c r="BQ6">
-        <v>0</v>
-      </c>
-      <c r="BR6">
-        <v>0</v>
-      </c>
-      <c r="BS6">
-        <v>0</v>
-      </c>
-      <c r="BT6">
-        <v>0</v>
-      </c>
-      <c r="BU6">
-        <v>0</v>
-      </c>
-      <c r="BV6">
-        <v>0</v>
-      </c>
-      <c r="BW6">
-        <v>0</v>
-      </c>
-      <c r="BX6">
-        <v>0</v>
-      </c>
-      <c r="BY6">
-        <v>0</v>
-      </c>
-      <c r="BZ6">
-        <v>0</v>
-      </c>
-      <c r="CA6">
-        <v>0</v>
-      </c>
-      <c r="CB6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CB7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CB1 A2:CB3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2312,7 +1275,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319190FD-FD72-4751-8599-FDB1FF03ABA9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28B630E2-4E60-4F5A-84F7-4889791F54B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -2331,7 +1294,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1CBB147-C6F6-4698-AFA8-62992EEFE699}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13114B45-8A70-4B42-82D2-45BE2B47AA7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -2342,7 +1305,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48D00D19-7C52-46C6-8D43-E417AB68CFB6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B95621F-3127-4E6F-B129-17E16E296945}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>

--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_8E1F44B0599B5389FE26624A271CB3BF095CFE13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13727F7D-4F34-4BDB-98EA-DF82AA16C451}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_314787AECB1B50BD9EB4E8188F8F8DC121BCF113" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE4BC5DE-A698-4CE2-8EBA-A7B946D3B815}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>RPRO</t>
   </si>
@@ -59,12 +59,81 @@
     <t>created_at</t>
   </si>
   <si>
+    <t>RPRO-250626-0096</t>
+  </si>
+  <si>
+    <t>Men's</t>
+  </si>
+  <si>
     <t>DIE-CUT</t>
   </si>
   <si>
+    <t>JV1-0695-3(arch skive)</t>
+  </si>
+  <si>
+    <t>145-17-00 LJ-B1-1-VEPM5 44" 180G</t>
+  </si>
+  <si>
+    <t>DC-010097</t>
+  </si>
+  <si>
+    <t>23/07/2025 13:25:54</t>
+  </si>
+  <si>
+    <t>RPRO-250526-0514</t>
+  </si>
+  <si>
     <t>Women's</t>
   </si>
   <si>
+    <t>OE-0198</t>
+  </si>
+  <si>
+    <t>QD-39 (M-0502)</t>
+  </si>
+  <si>
+    <t>71R EPM MERRY MESH(LJB-730) 44" 220G</t>
+  </si>
+  <si>
+    <t>OE-007434</t>
+  </si>
+  <si>
+    <t>23/07/2025 14:24:36</t>
+  </si>
+  <si>
+    <t>RPRO-250610-0389</t>
+  </si>
+  <si>
+    <t>OV-0256</t>
+  </si>
+  <si>
+    <t>21-005-M-Low (M-0235)</t>
+  </si>
+  <si>
+    <t>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-008378</t>
+  </si>
+  <si>
+    <t>23/07/2025 16:19:54</t>
+  </si>
+  <si>
+    <t>RPRO-250606-0428</t>
+  </si>
+  <si>
+    <t>ON-112 (M-0236)</t>
+  </si>
+  <si>
+    <t>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-008350</t>
+  </si>
+  <si>
+    <t>23/07/2025 22:26:03</t>
+  </si>
+  <si>
     <t>RPRO-250627-0145</t>
   </si>
   <si>
@@ -77,7 +146,7 @@
     <t>DC-011263</t>
   </si>
   <si>
-    <t>24/07/2025 05:58:44</t>
+    <t>23/07/2025 22:58:44</t>
   </si>
 </sst>
 </file>
@@ -454,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
@@ -744,13 +813,13 @@
     </row>
     <row r="2" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -762,7 +831,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
@@ -801,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -813,181 +882,1149 @@
         <v>0</v>
       </c>
       <c r="X2">
+        <v>7</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="BZ2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>25</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>0</v>
-      </c>
-      <c r="BC2">
-        <v>0</v>
-      </c>
-      <c r="BD2">
-        <v>0</v>
-      </c>
-      <c r="BE2">
-        <v>0</v>
-      </c>
-      <c r="BF2">
-        <v>0</v>
-      </c>
-      <c r="BG2">
-        <v>0</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>0</v>
-      </c>
-      <c r="BR2">
-        <v>0</v>
-      </c>
-      <c r="BS2">
-        <v>0</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2">
-        <v>0</v>
-      </c>
-      <c r="BZ2">
-        <v>0</v>
-      </c>
-      <c r="CA2">
-        <v>0</v>
-      </c>
-      <c r="CB2">
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CB1 A2:CB3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CB7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1275,7 +2312,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28B630E2-4E60-4F5A-84F7-4889791F54B8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92944EE4-13BB-4C55-A024-EECBE4048E9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1294,7 +2331,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13114B45-8A70-4B42-82D2-45BE2B47AA7B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2657351-AF9F-4D38-B186-0F4CF5564E58}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -1305,7 +2342,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B95621F-3127-4E6F-B129-17E16E296945}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DCF60C7-E13B-4DDA-B7B5-6008144071E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>

--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -1,159 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ortholitevietnam.sharepoint.com/sites/production9/Shared Documents/PRODUCTION/TRUONG OFFICE/WEEKLY REPORT/WE ARE BETTER/vercel-dashboard/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_314787AECB1B50BD9EB4E8188F8F8DC121BCF113" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE4BC5DE-A698-4CE2-8EBA-A7B946D3B815}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Supplement" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
-  <si>
-    <t>RPRO</t>
-  </si>
-  <si>
-    <t>Giới tính</t>
-  </si>
-  <si>
-    <t>Mã khuôn</t>
-  </si>
-  <si>
-    <t>Mã dao</t>
-  </si>
-  <si>
-    <t>Vải</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>created_at</t>
-  </si>
-  <si>
-    <t>RPRO-250626-0096</t>
-  </si>
-  <si>
-    <t>Men's</t>
-  </si>
-  <si>
-    <t>DIE-CUT</t>
-  </si>
-  <si>
-    <t>JV1-0695-3(arch skive)</t>
-  </si>
-  <si>
-    <t>145-17-00 LJ-B1-1-VEPM5 44" 180G</t>
-  </si>
-  <si>
-    <t>DC-010097</t>
-  </si>
-  <si>
-    <t>23/07/2025 13:25:54</t>
-  </si>
-  <si>
-    <t>RPRO-250526-0514</t>
-  </si>
-  <si>
-    <t>Women's</t>
-  </si>
-  <si>
-    <t>OE-0198</t>
-  </si>
-  <si>
-    <t>QD-39 (M-0502)</t>
-  </si>
-  <si>
-    <t>71R EPM MERRY MESH(LJB-730) 44" 220G</t>
-  </si>
-  <si>
-    <t>OE-007434</t>
-  </si>
-  <si>
-    <t>23/07/2025 14:24:36</t>
-  </si>
-  <si>
-    <t>RPRO-250610-0389</t>
-  </si>
-  <si>
-    <t>OV-0256</t>
-  </si>
-  <si>
-    <t>21-005-M-Low (M-0235)</t>
-  </si>
-  <si>
-    <t>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
-  </si>
-  <si>
-    <t>OV-008378</t>
-  </si>
-  <si>
-    <t>23/07/2025 16:19:54</t>
-  </si>
-  <si>
-    <t>RPRO-250606-0428</t>
-  </si>
-  <si>
-    <t>ON-112 (M-0236)</t>
-  </si>
-  <si>
-    <t>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
-  </si>
-  <si>
-    <t>OV-008350</t>
-  </si>
-  <si>
-    <t>23/07/2025 22:26:03</t>
-  </si>
-  <si>
-    <t>RPRO-250627-0145</t>
-  </si>
-  <si>
-    <t>QA-7H (D-0256) (skive arch)</t>
-  </si>
-  <si>
-    <t>10A (PP)LINING KNIT MATTE MICRO (HOOD) REC 44" 250G</t>
-  </si>
-  <si>
-    <t>DC-011263</t>
-  </si>
-  <si>
-    <t>23/07/2025 22:58:44</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -183,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -522,199 +396,195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CB6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:CB10"/>
   <sheetData>
-    <row r="1" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>RPRO</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Giới tính</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Mã khuôn</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Mã dao</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Vải</v>
+      </c>
+      <c r="F1" t="str">
+        <v>BOM</v>
+      </c>
+      <c r="G1" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="H1" t="str">
+        <v>created_at</v>
       </c>
       <c r="I1">
         <v>1</v>
       </c>
       <c r="J1">
-        <f t="shared" ref="J1:AW1" si="0">I1+0.5</f>
+        <f>I1+0.5</f>
         <v>1.5</v>
       </c>
       <c r="K1">
-        <f t="shared" si="0"/>
+        <f>J1+0.5</f>
         <v>2</v>
       </c>
       <c r="L1">
-        <f t="shared" si="0"/>
+        <f>K1+0.5</f>
         <v>2.5</v>
       </c>
       <c r="M1">
-        <f t="shared" si="0"/>
+        <f>L1+0.5</f>
         <v>3</v>
       </c>
       <c r="N1">
-        <f t="shared" si="0"/>
+        <f>M1+0.5</f>
         <v>3.5</v>
       </c>
       <c r="O1">
-        <f t="shared" si="0"/>
+        <f>N1+0.5</f>
         <v>4</v>
       </c>
       <c r="P1">
-        <f t="shared" si="0"/>
+        <f>O1+0.5</f>
         <v>4.5</v>
       </c>
       <c r="Q1">
-        <f t="shared" si="0"/>
+        <f>P1+0.5</f>
         <v>5</v>
       </c>
       <c r="R1">
-        <f t="shared" si="0"/>
+        <f>Q1+0.5</f>
         <v>5.5</v>
       </c>
       <c r="S1">
-        <f t="shared" si="0"/>
+        <f>R1+0.5</f>
         <v>6</v>
       </c>
       <c r="T1">
-        <f t="shared" si="0"/>
+        <f>S1+0.5</f>
         <v>6.5</v>
       </c>
       <c r="U1">
-        <f t="shared" si="0"/>
+        <f>T1+0.5</f>
         <v>7</v>
       </c>
       <c r="V1">
-        <f t="shared" si="0"/>
+        <f>U1+0.5</f>
         <v>7.5</v>
       </c>
       <c r="W1">
-        <f t="shared" si="0"/>
+        <f>V1+0.5</f>
         <v>8</v>
       </c>
       <c r="X1">
-        <f t="shared" si="0"/>
+        <f>W1+0.5</f>
         <v>8.5</v>
       </c>
       <c r="Y1">
-        <f t="shared" si="0"/>
+        <f>X1+0.5</f>
         <v>9</v>
       </c>
       <c r="Z1">
-        <f t="shared" si="0"/>
+        <f>Y1+0.5</f>
         <v>9.5</v>
       </c>
       <c r="AA1">
-        <f t="shared" si="0"/>
+        <f>Z1+0.5</f>
         <v>10</v>
       </c>
       <c r="AB1">
-        <f t="shared" si="0"/>
+        <f>AA1+0.5</f>
         <v>10.5</v>
       </c>
       <c r="AC1">
-        <f t="shared" si="0"/>
+        <f>AB1+0.5</f>
         <v>11</v>
       </c>
       <c r="AD1">
-        <f t="shared" si="0"/>
+        <f>AC1+0.5</f>
         <v>11.5</v>
       </c>
       <c r="AE1">
-        <f t="shared" si="0"/>
+        <f>AD1+0.5</f>
         <v>12</v>
       </c>
       <c r="AF1">
-        <f t="shared" si="0"/>
+        <f>AE1+0.5</f>
         <v>12.5</v>
       </c>
       <c r="AG1">
-        <f t="shared" si="0"/>
+        <f>AF1+0.5</f>
         <v>13</v>
       </c>
       <c r="AH1">
-        <f t="shared" si="0"/>
+        <f>AG1+0.5</f>
         <v>13.5</v>
       </c>
       <c r="AI1">
-        <f t="shared" si="0"/>
+        <f>AH1+0.5</f>
         <v>14</v>
       </c>
       <c r="AJ1">
-        <f t="shared" si="0"/>
+        <f>AI1+0.5</f>
         <v>14.5</v>
       </c>
       <c r="AK1">
-        <f t="shared" si="0"/>
+        <f>AJ1+0.5</f>
         <v>15</v>
       </c>
       <c r="AL1">
-        <f t="shared" si="0"/>
+        <f>AK1+0.5</f>
         <v>15.5</v>
       </c>
       <c r="AM1">
-        <f t="shared" si="0"/>
+        <f>AL1+0.5</f>
         <v>16</v>
       </c>
       <c r="AN1">
-        <f t="shared" si="0"/>
+        <f>AM1+0.5</f>
         <v>16.5</v>
       </c>
       <c r="AO1">
-        <f t="shared" si="0"/>
+        <f>AN1+0.5</f>
         <v>17</v>
       </c>
       <c r="AP1">
-        <f t="shared" si="0"/>
+        <f>AO1+0.5</f>
         <v>17.5</v>
       </c>
       <c r="AQ1">
-        <f t="shared" si="0"/>
+        <f>AP1+0.5</f>
         <v>18</v>
       </c>
       <c r="AR1">
-        <f t="shared" si="0"/>
+        <f>AQ1+0.5</f>
         <v>18.5</v>
       </c>
       <c r="AS1">
-        <f t="shared" si="0"/>
+        <f>AR1+0.5</f>
         <v>19</v>
       </c>
       <c r="AT1">
-        <f t="shared" si="0"/>
+        <f>AS1+0.5</f>
         <v>19.5</v>
       </c>
       <c r="AU1">
-        <f t="shared" si="0"/>
+        <f>AT1+0.5</f>
         <v>20</v>
       </c>
       <c r="AV1">
-        <f t="shared" si="0"/>
+        <f>AU1+0.5</f>
         <v>20.5</v>
       </c>
       <c r="AW1">
-        <f t="shared" si="0"/>
+        <f>AV1+0.5</f>
         <v>21</v>
       </c>
       <c r="AX1">
@@ -811,30 +681,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>RPRO-250626-0096</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Men's</v>
+      </c>
+      <c r="C2" t="str">
+        <v>DIE-CUT</v>
+      </c>
+      <c r="D2" t="str">
+        <v>JV1-0695-3(arch skive)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>145-17-00 LJ-B1-1-VEPM5 44" 180G</v>
+      </c>
+      <c r="F2" t="str">
+        <v>DC-010097</v>
       </c>
       <c r="G2">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
+      <c r="H2" t="str">
+        <v>23/07/2025 13:25:54</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1053,30 +923,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>RPRO-250526-0514</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Women's</v>
+      </c>
+      <c r="C3" t="str">
+        <v>OE-0198</v>
+      </c>
+      <c r="D3" t="str">
+        <v>QD-39 (M-0502)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>71R EPM MERRY MESH(LJB-730) 44" 220G</v>
+      </c>
+      <c r="F3" t="str">
+        <v>OE-007434</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
+      <c r="H3" t="str">
+        <v>23/07/2025 14:24:36</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1295,30 +1165,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>RPRO-250610-0389</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Men's</v>
+      </c>
+      <c r="C4" t="str">
+        <v>OV-0256</v>
+      </c>
+      <c r="D4" t="str">
+        <v>21-005-M-Low (M-0235)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
+      </c>
+      <c r="F4" t="str">
+        <v>OV-008378</v>
       </c>
       <c r="G4">
         <v>26</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
+      <c r="H4" t="str">
+        <v>23/07/2025 16:19:54</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1537,30 +1407,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>RPRO-250606-0428</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Men's</v>
+      </c>
+      <c r="C5" t="str">
+        <v>OV-0256</v>
+      </c>
+      <c r="D5" t="str">
+        <v>ON-112 (M-0236)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
+      </c>
+      <c r="F5" t="str">
+        <v>OV-008350</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5" t="s">
-        <v>32</v>
+      <c r="H5" t="str">
+        <v>23/07/2025 22:26:03</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1779,30 +1649,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>RPRO-250627-0145</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Women's</v>
+      </c>
+      <c r="C6" t="str">
+        <v>DIE-CUT</v>
+      </c>
+      <c r="D6" t="str">
+        <v>QA-7H (D-0256) (skive arch)</v>
+      </c>
+      <c r="E6" t="str">
+        <v>10A (PP)LINING KNIT MATTE MICRO (HOOD) REC 44" 250G</v>
+      </c>
+      <c r="F6" t="str">
+        <v>DC-011263</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>37</v>
+      <c r="H6" t="str">
+        <v>23/07/2025 22:58:44</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2018,13 +1888,739 @@
         <v>0</v>
       </c>
       <c r="CB6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>RPRO-250606-0433</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Women's</v>
+      </c>
+      <c r="C7" t="str">
+        <v>OV-0256</v>
+      </c>
+      <c r="D7" t="str">
+        <v>ON-112 (M-0236)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>11-4202TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
+      </c>
+      <c r="F7" t="str">
+        <v>OV-007210</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v>23/07/2025 23:39:58</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>8</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>RPRO-250610-0266</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Women's</v>
+      </c>
+      <c r="C8" t="str">
+        <v>OV-0256</v>
+      </c>
+      <c r="D8" t="str">
+        <v>21-005-W-Low (M-0234)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>18-4006TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
+      </c>
+      <c r="F8" t="str">
+        <v>OV-007160</v>
+      </c>
+      <c r="G8">
+        <v>210</v>
+      </c>
+      <c r="H8" t="str">
+        <v>24/07/2025 08:23:48</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>55</v>
+      </c>
+      <c r="T8">
+        <v>55</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>RPRO-250610-0514</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Women's</v>
+      </c>
+      <c r="C9" t="str">
+        <v>OV-0377</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ON-8-W-2 (M-0418)</v>
+      </c>
+      <c r="E9" t="str">
+        <v>11-4202TCX YH-S960 EPM5 (100% Recycled PET) 44'' 198G</v>
+      </c>
+      <c r="F9" t="str">
+        <v>OV-008950</v>
+      </c>
+      <c r="G9">
+        <v>23</v>
+      </c>
+      <c r="H9" t="str">
+        <v>24/07/2025 09:07:49</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>6</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>15</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CB7" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CB10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2291,6 +2887,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e">
@@ -2302,49 +2907,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92944EE4-13BB-4C55-A024-EECBE4048E9C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31919BC8-9379-4D37-B41C-E8135171CD65}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2657351-AF9F-4D38-B186-0F4CF5564E58}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
-    <ds:schemaRef ds:uri="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78549BE0-398A-4CF5-810D-3FEC6A11E863}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DCF60C7-E13B-4DDA-B7B5-6008144071E5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{990668BE-81DE-4D4D-B33A-408178725769}"/>
 </file>
--- a/data/Supplement.xlsx
+++ b/data/Supplement.xlsx
@@ -1,40 +1,201 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_3149407D34AAD0E3C6A7FEF72B9A1564395F9124" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC6CB8D2-9852-434A-BFBC-8172FFCD6E6D}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Supplement" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
+  <si>
+    <t>RPRO</t>
+  </si>
+  <si>
+    <t>Giới tính</t>
+  </si>
+  <si>
+    <t>Mã khuôn</t>
+  </si>
+  <si>
+    <t>Mã dao</t>
+  </si>
+  <si>
+    <t>Vải</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>RPRO-250626-0096</t>
+  </si>
+  <si>
+    <t>Men's</t>
+  </si>
+  <si>
+    <t>DIE-CUT</t>
+  </si>
+  <si>
+    <t>JV1-0695-3(arch skive)</t>
+  </si>
+  <si>
+    <t>145-17-00 LJ-B1-1-VEPM5 44" 180G</t>
+  </si>
+  <si>
+    <t>DC-010097</t>
+  </si>
+  <si>
+    <t>23/07/2025 13:25:54</t>
+  </si>
+  <si>
+    <t>RPRO-250526-0514</t>
+  </si>
+  <si>
+    <t>Women's</t>
+  </si>
+  <si>
+    <t>OE-0198</t>
+  </si>
+  <si>
+    <t>QD-39 (M-0502)</t>
+  </si>
+  <si>
+    <t>71R EPM MERRY MESH(LJB-730) 44" 220G</t>
+  </si>
+  <si>
+    <t>OE-007434</t>
+  </si>
+  <si>
+    <t>23/07/2025 14:24:36</t>
+  </si>
+  <si>
+    <t>RPRO-250610-0389</t>
+  </si>
+  <si>
+    <t>OV-0256</t>
+  </si>
+  <si>
+    <t>21-005-M-Low (M-0235)</t>
+  </si>
+  <si>
+    <t>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-008378</t>
+  </si>
+  <si>
+    <t>23/07/2025 16:19:54</t>
+  </si>
+  <si>
+    <t>RPRO-250606-0428</t>
+  </si>
+  <si>
+    <t>ON-112 (M-0236)</t>
+  </si>
+  <si>
+    <t>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-008350</t>
+  </si>
+  <si>
+    <t>23/07/2025 22:26:03</t>
+  </si>
+  <si>
+    <t>RPRO-250627-0145</t>
+  </si>
+  <si>
+    <t>QA-7H (D-0256) (skive arch)</t>
+  </si>
+  <si>
+    <t>10A (PP)LINING KNIT MATTE MICRO (HOOD) REC 44" 250G</t>
+  </si>
+  <si>
+    <t>DC-011263</t>
+  </si>
+  <si>
+    <t>23/07/2025 22:58:44</t>
+  </si>
+  <si>
+    <t>RPRO-250606-0433</t>
+  </si>
+  <si>
+    <t>11-4202TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-007210</t>
+  </si>
+  <si>
+    <t>23/07/2025 23:39:58</t>
+  </si>
+  <si>
+    <t>RPRO-250610-0266</t>
+  </si>
+  <si>
+    <t>21-005-W-Low (M-0234)</t>
+  </si>
+  <si>
+    <t>18-4006TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</t>
+  </si>
+  <si>
+    <t>OV-007160</t>
+  </si>
+  <si>
+    <t>24/07/2025 08:23:48</t>
+  </si>
+  <si>
+    <t>RPRO-250610-0514</t>
+  </si>
+  <si>
+    <t>OV-0377</t>
+  </si>
+  <si>
+    <t>ON-8-W-2 (M-0418)</t>
+  </si>
+  <si>
+    <t>11-4202TCX YH-S960 EPM5 (100% Recycled PET) 44'' 198G</t>
+  </si>
+  <si>
+    <t>OV-008950</t>
+  </si>
+  <si>
+    <t>24/07/2025 09:07:49</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1">
     <font>
       <sz val="12"/>
@@ -65,13 +226,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,33 +565,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:CB9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>RPRO</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Giới tính</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Mã khuôn</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Mã dao</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Vải</v>
-      </c>
-      <c r="F1" t="str">
-        <v>BOM</v>
-      </c>
-      <c r="G1" t="str">
-        <v>TOTAL</v>
-      </c>
-      <c r="H1" t="str">
-        <v>created_at</v>
+    <row r="1" spans="1:80">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
       <c r="I1">
         <v>1</v>
@@ -681,30 +851,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>RPRO-250626-0096</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C2" t="str">
-        <v>DIE-CUT</v>
-      </c>
-      <c r="D2" t="str">
-        <v>JV1-0695-3(arch skive)</v>
-      </c>
-      <c r="E2" t="str">
-        <v>145-17-00 LJ-B1-1-VEPM5 44" 180G</v>
-      </c>
-      <c r="F2" t="str">
-        <v>DC-010097</v>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
       </c>
       <c r="G2">
         <v>11</v>
       </c>
-      <c r="H2" t="str">
-        <v>23/07/2025 13:25:54</v>
+      <c r="H2" t="s">
+        <v>14</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -923,30 +1093,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>RPRO-250526-0514</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Women's</v>
-      </c>
-      <c r="C3" t="str">
-        <v>OE-0198</v>
-      </c>
-      <c r="D3" t="str">
-        <v>QD-39 (M-0502)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>71R EPM MERRY MESH(LJB-730) 44" 220G</v>
-      </c>
-      <c r="F3" t="str">
-        <v>OE-007434</v>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" t="str">
-        <v>23/07/2025 14:24:36</v>
+      <c r="H3" t="s">
+        <v>21</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1165,30 +1335,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>RPRO-250610-0389</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C4" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D4" t="str">
-        <v>21-005-M-Low (M-0235)</v>
-      </c>
-      <c r="E4" t="str">
-        <v>19-1624TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F4" t="str">
-        <v>OV-008378</v>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
       </c>
       <c r="G4">
         <v>26</v>
       </c>
-      <c r="H4" t="str">
-        <v>23/07/2025 16:19:54</v>
+      <c r="H4" t="s">
+        <v>27</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1407,30 +1577,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>RPRO-250606-0428</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Men's</v>
-      </c>
-      <c r="C5" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D5" t="str">
-        <v>ON-112 (M-0236)</v>
-      </c>
-      <c r="E5" t="str">
-        <v>19-3911TCX YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F5" t="str">
-        <v>OV-008350</v>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5" t="str">
-        <v>23/07/2025 22:26:03</v>
+      <c r="H5" t="s">
+        <v>32</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1649,30 +1819,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>RPRO-250627-0145</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Women's</v>
-      </c>
-      <c r="C6" t="str">
-        <v>DIE-CUT</v>
-      </c>
-      <c r="D6" t="str">
-        <v>QA-7H (D-0256) (skive arch)</v>
-      </c>
-      <c r="E6" t="str">
-        <v>10A (PP)LINING KNIT MATTE MICRO (HOOD) REC 44" 250G</v>
-      </c>
-      <c r="F6" t="str">
-        <v>DC-011263</v>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" t="str">
-        <v>23/07/2025 22:58:44</v>
+      <c r="H6" t="s">
+        <v>37</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1891,30 +2061,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>RPRO-250606-0433</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Women's</v>
-      </c>
-      <c r="C7" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D7" t="str">
-        <v>ON-112 (M-0236)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>11-4202TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F7" t="str">
-        <v>OV-007210</v>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" t="str">
-        <v>23/07/2025 23:39:58</v>
+      <c r="H7" t="s">
+        <v>41</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2133,30 +2303,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>RPRO-250610-0266</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Women's</v>
-      </c>
-      <c r="C8" t="str">
-        <v>OV-0256</v>
-      </c>
-      <c r="D8" t="str">
-        <v>21-005-W-Low (M-0234)</v>
-      </c>
-      <c r="E8" t="str">
-        <v>18-4006TPG YH-S817A EPM5 (100% REC.PES) 44" 220G</v>
-      </c>
-      <c r="F8" t="str">
-        <v>OV-007160</v>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
       </c>
       <c r="G8">
         <v>210</v>
       </c>
-      <c r="H8" t="str">
-        <v>24/07/2025 08:23:48</v>
+      <c r="H8" t="s">
+        <v>46</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2375,30 +2545,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>RPRO-250610-0514</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Women's</v>
-      </c>
-      <c r="C9" t="str">
-        <v>OV-0377</v>
-      </c>
-      <c r="D9" t="str">
-        <v>ON-8-W-2 (M-0418)</v>
-      </c>
-      <c r="E9" t="str">
-        <v>11-4202TCX YH-S960 EPM5 (100% Recycled PET) 44'' 198G</v>
-      </c>
-      <c r="F9" t="str">
-        <v>OV-008950</v>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
       </c>
       <c r="G9">
         <v>23</v>
       </c>
-      <c r="H9" t="str">
-        <v>24/07/2025 09:07:49</v>
+      <c r="H9" t="s">
+        <v>52</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2620,14 +2790,23 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CB10"/>
+    <ignoredError sqref="A1:CB10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00a272c57818f5a2598402ed9b64a3e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb7fe868ff501d2f097cc8d8c004abe7" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ABA881C598A1DC4096D4B66B961FB704" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="63da96a68aea1e0a95bb00dc613529db">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e" xmlns:ns3="71b44b8b-5734-40bc-bcd6-983774da7c1c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bc38e99d4a2ab748d495d1563ca7dbf9" ns2:_="" ns3:_="">
     <xsd:import namespace="b65cb79d-c821-4d3d-aab2-5ef15e9cc85e"/>
     <xsd:import namespace="71b44b8b-5734-40bc-bcd6-983774da7c1c"/>
     <xsd:element name="properties">
@@ -2654,6 +2833,7 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2741,6 +2921,11 @@
       </xsd:simpleType>
     </xsd:element>
     <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="27" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
@@ -2886,15 +3071,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2908,11 +3084,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31919BC8-9379-4D37-B41C-E8135171CD65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78549BE0-398A-4CF5-810D-3FEC6A11E863}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78549BE0-398A-4CF5-810D-3FEC6A11E863}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E9D90A7-B992-4CC5-892A-22FF1C23215E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
